--- a/data/excel/20260617_selection.xlsx
+++ b/data/excel/20260617_selection.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +77,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
         <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -107,7 +130,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +521,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 0 只入选</t>
         </is>
       </c>
     </row>
@@ -525,7 +560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 0 只入选</t>
         </is>
       </c>
     </row>
@@ -564,7 +599,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 0 只入选</t>
         </is>
       </c>
     </row>
@@ -603,7 +638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 0 只入选</t>
         </is>
       </c>
     </row>
@@ -629,8 +664,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -642,14 +691,1269 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 30 只入选</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>无符合条件标的</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>main_inflow</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>momentum_5d</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>catalyst_score</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>big_buy_ratio</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>turnover_rate</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>base_score</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>formula_score</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>total_score</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>penalty_log</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>000564.SZ</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>24349.3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>供销大集</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>000066.SZ</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>11881.82</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>中国长城</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>000593.SZ</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1589.73</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>德龙汇能</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>301072.SZ</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1135.06</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>中捷精工</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>688685.SH</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1435.9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>迈信林</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>301070.SZ</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>8735.299999999999</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>开勒股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>000697.SZ</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1505.63</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>炼石航空</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>688625.SH</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5452.03</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.4663</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>呈和科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>688693.SH</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>420.25</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>锴威特</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>600416.SH</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1135.41</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>湘电股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>002848.SZ</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1007.58</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.4853</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>高斯贝尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>688141.SH</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>16030.44</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.6698</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>杰华特</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>688112.SH</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>4761.6</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>鼎阳科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>600615.SH</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>鑫源智造</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>600378.SH</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>7325</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>XD昊华科</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>600641.SH</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>先导基电</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>600403.SH</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4092.83</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-17.86</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>大有能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>002696.SZ</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>248.25</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.6313</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>百洋股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>002709.SZ</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>95943.09</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>天赐材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>002682.SZ</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>龙洲股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>600605.SH</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>3581.83</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>汇通能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>002729.SZ</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>好利科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>600592.SH</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>1608.28</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-20.78</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.4798</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>龙溪股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>600478.SH</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>6757.7</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.5966</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>科力远</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>600487.SH</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>118241.69</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>688167.SH</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>30472.29</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>炬光科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>600293.SH</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2127.42</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>三峡新材</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>600301.SH</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>12039</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>华锡有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>600228.SH</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2284.96</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>返利科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>301389.SZ</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>19835.9</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>隆扬电子</t>
         </is>
       </c>
     </row>
@@ -681,7 +1985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 0 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 0 只入选</t>
         </is>
       </c>
     </row>
@@ -728,7 +2032,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 1 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 1 只入选</t>
         </is>
       </c>
     </row>
@@ -765,30 +2069,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>弱转强</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>rzq</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>639f08f73cd6</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-17T05:50:34.526496</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>强转弱反抽</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>qzrfc</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>c3a268fe813e</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-17T06:26:15.787635</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -826,7 +2130,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>策略: rzq | run_id: 639f08f73cd6 | 开始: 2026-06-17T05:50:34.526496 | 共 5 只入选</t>
+          <t>策略: qzrfc | run_id: c3a268fe813e | 开始: 2026-06-17T06:26:15.787635 | 共 5 只入选</t>
         </is>
       </c>
     </row>
@@ -853,84 +2157,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>load_data</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
+      <c r="C4" s="6" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>clean_data</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="C5" s="6" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>calc_factors</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>filter_sort</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
